--- a/backend/expense_details.xlsx
+++ b/backend/expense_details.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Income" sheetId="1" r:id="rId1"/>
+    <sheet name="Expense" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -64,9 +64,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -398,77 +397,109 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:D7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>category</v>
+        <v>STT</v>
       </c>
       <c r="B1" t="str">
-        <v>amount</v>
+        <v>Danh mục</v>
       </c>
       <c r="C1" t="str">
-        <v>Date</v>
+        <v>Số tiền</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Ngày tháng</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="str">
+        <v>đi chơi</v>
+      </c>
+      <c r="C2">
+        <v>100001</v>
+      </c>
+      <c r="D2" t="str">
+        <v>9/5/2026</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="str">
+        <v>đi chơi</v>
+      </c>
+      <c r="C3">
+        <v>100000</v>
+      </c>
+      <c r="D3" t="str">
+        <v>10/4/2026</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="str">
         <v>di date</v>
       </c>
-      <c r="B2">
+      <c r="C4">
         <v>500</v>
       </c>
-      <c r="C2" s="1">
-        <v>46115.00034722222</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
+      <c r="D4" t="str">
+        <v>3/4/2026</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="str">
         <v>di caffe</v>
       </c>
-      <c r="B3">
+      <c r="C5">
         <v>100</v>
       </c>
-      <c r="C3" s="1">
-        <v>46115.00034722222</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
+      <c r="D5" t="str">
+        <v>3/4/2026</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="str">
         <v>di kake</v>
       </c>
-      <c r="B4">
+      <c r="C6">
         <v>100</v>
       </c>
-      <c r="C4" s="1">
-        <v>46115.00034722222</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>banh mi</v>
-      </c>
-      <c r="B5">
+      <c r="D6" t="str">
+        <v>3/4/2026</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="str">
+        <v>di date</v>
+      </c>
+      <c r="C7">
         <v>300</v>
       </c>
-      <c r="C5" s="1">
-        <v>46085.00034722222</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>di date</v>
-      </c>
-      <c r="B6">
-        <v>300</v>
-      </c>
-      <c r="C6" s="1">
-        <v>46085.00034722222</v>
+      <c r="D7" t="str">
+        <v>4/3/2026</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D7"/>
   </ignoredErrors>
 </worksheet>
 </file>